--- a/Anexo_A_Datos_Consumo.xlsx
+++ b/Anexo_A_Datos_Consumo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\franc\OneDrive\Documentos\SolucionesEnergeticasParaWSN\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\omich\Documents\SolucionesEnergeticasParaWSN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CB2682C-3EDD-4461-8D75-292414EB46EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B080AE0-6226-4794-B8B6-959AB8A4B573}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{16E32420-E92C-48F4-9AFE-AC6FE85723F6}"/>
   </bookViews>
@@ -135,7 +135,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -12066,22 +12066,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3FA4C8B-A099-47B7-BA2E-F5A7D41331DF}">
   <dimension ref="A1:O38"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.59765625" defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.59765625" style="4"/>
-    <col min="3" max="3" width="28.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.796875" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="11.59765625" style="4"/>
-    <col min="8" max="8" width="11.3984375" style="4" customWidth="1"/>
-    <col min="9" max="9" width="11.59765625" style="4"/>
-    <col min="10" max="10" width="29.19921875" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="30.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.8984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.19921875" style="4" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="11.59765625" style="4"/>
+    <col min="1" max="2" width="11.5546875" style="4"/>
+    <col min="3" max="3" width="28.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="11.5546875" style="4"/>
+    <col min="8" max="8" width="11.44140625" style="4" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" style="4"/>
+    <col min="10" max="10" width="29.21875" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="23.21875" style="4" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="11.5546875" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
@@ -12101,7 +12101,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
@@ -12142,7 +12142,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="str">
         <f>C3 &amp;" "&amp;E3</f>
         <v>BASICO LoRa</v>
@@ -12193,7 +12193,7 @@
       </c>
       <c r="O3" s="28"/>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="str">
         <f t="shared" ref="A4:A38" si="0">C4 &amp;" "&amp;E4</f>
         <v>BASICO LoRa</v>
@@ -12244,7 +12244,7 @@
       </c>
       <c r="O4" s="28"/>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ADAPTIVE LoRa</v>
@@ -12295,7 +12295,7 @@
       </c>
       <c r="O5" s="28"/>
     </row>
-    <row r="6" spans="1:15">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ADAPTIVE LoRa</v>
@@ -12346,7 +12346,7 @@
       </c>
       <c r="O6" s="28"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ENERGY LoRa</v>
@@ -12397,7 +12397,7 @@
       </c>
       <c r="O7" s="28"/>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ENERGY + ADAPTIVE LoRa</v>
@@ -12448,7 +12448,7 @@
       </c>
       <c r="O8" s="28"/>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ADAPTIVE + CODEC LoRa</v>
@@ -12499,7 +12499,7 @@
       </c>
       <c r="O9" s="28"/>
     </row>
-    <row r="10" spans="1:15">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ADAPTIVE + CODEC LoRa</v>
@@ -12550,7 +12550,7 @@
       </c>
       <c r="O10" s="28"/>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="str">
         <f t="shared" si="0"/>
         <v>CODEC LoRa</v>
@@ -12601,7 +12601,7 @@
       </c>
       <c r="O11" s="28"/>
     </row>
-    <row r="12" spans="1:15">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="str">
         <f t="shared" si="0"/>
         <v>CODEC LoRa</v>
@@ -12652,7 +12652,7 @@
       </c>
       <c r="O12" s="28"/>
     </row>
-    <row r="13" spans="1:15">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="str">
         <f t="shared" si="0"/>
         <v>CODEC + ENERGY LoRa</v>
@@ -12703,7 +12703,7 @@
       </c>
       <c r="O13" s="28"/>
     </row>
-    <row r="14" spans="1:15">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="str">
         <f t="shared" si="0"/>
         <v>CODEC + ENERGY + ADAPTIVE LoRa</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="O14" s="28"/>
     </row>
-    <row r="15" spans="1:15">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="str">
         <f t="shared" si="0"/>
         <v>BASICO NRF24L01</v>
@@ -12805,7 +12805,7 @@
       </c>
       <c r="O15" s="28"/>
     </row>
-    <row r="16" spans="1:15">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="str">
         <f t="shared" si="0"/>
         <v>BASICO NRF24L01</v>
@@ -12856,7 +12856,7 @@
       </c>
       <c r="O16" s="28"/>
     </row>
-    <row r="17" spans="1:15">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ADAPTIVE NRF24L01</v>
@@ -12907,7 +12907,7 @@
       </c>
       <c r="O17" s="28"/>
     </row>
-    <row r="18" spans="1:15">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ADAPTIVE NRF24L01</v>
@@ -12958,7 +12958,7 @@
       </c>
       <c r="O18" s="28"/>
     </row>
-    <row r="19" spans="1:15">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ENERGY NRF24L01</v>
@@ -13009,7 +13009,7 @@
       </c>
       <c r="O19" s="28"/>
     </row>
-    <row r="20" spans="1:15">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ENERGY + ADAPTIVE NRF24L01</v>
@@ -13060,7 +13060,7 @@
       </c>
       <c r="O20" s="28"/>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ADAPTIVE + CODEC NRF24L01</v>
@@ -13111,7 +13111,7 @@
       </c>
       <c r="O21" s="28"/>
     </row>
-    <row r="22" spans="1:15">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ADAPTIVE + CODEC NRF24L01</v>
@@ -13162,7 +13162,7 @@
       </c>
       <c r="O22" s="28"/>
     </row>
-    <row r="23" spans="1:15">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="str">
         <f t="shared" si="0"/>
         <v>CODEC NRF24L01</v>
@@ -13213,7 +13213,7 @@
       </c>
       <c r="O23" s="28"/>
     </row>
-    <row r="24" spans="1:15">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="4" t="str">
         <f t="shared" si="0"/>
         <v>CODEC NRF24L01</v>
@@ -13264,7 +13264,7 @@
       </c>
       <c r="O24" s="28"/>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="4" t="str">
         <f t="shared" si="0"/>
         <v>CODEC + ENERGY NRF24L01</v>
@@ -13315,7 +13315,7 @@
       </c>
       <c r="O25" s="28"/>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="4" t="str">
         <f t="shared" si="0"/>
         <v>CODEC + ENERGY + ADAPTATIVE NRF24L01</v>
@@ -13366,7 +13366,7 @@
       </c>
       <c r="O26" s="28"/>
     </row>
-    <row r="27" spans="1:15">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="4" t="str">
         <f t="shared" si="0"/>
         <v>BASICO XBEE</v>
@@ -13417,7 +13417,7 @@
       </c>
       <c r="O27" s="28"/>
     </row>
-    <row r="28" spans="1:15">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="str">
         <f t="shared" si="0"/>
         <v>BASICO XBEE</v>
@@ -13468,7 +13468,7 @@
       </c>
       <c r="O28" s="28"/>
     </row>
-    <row r="29" spans="1:15">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ADAPTIVE XBEE</v>
@@ -13519,7 +13519,7 @@
       </c>
       <c r="O29" s="28"/>
     </row>
-    <row r="30" spans="1:15">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ADAPTIVE XBEE</v>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="O30" s="28"/>
     </row>
-    <row r="31" spans="1:15">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ENERGY XBEE</v>
@@ -13621,7 +13621,7 @@
       </c>
       <c r="O31" s="28"/>
     </row>
-    <row r="32" spans="1:15">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ENERGY + ADAPTIVE XBEE</v>
@@ -13672,7 +13672,7 @@
       </c>
       <c r="O32" s="28"/>
     </row>
-    <row r="33" spans="1:15">
+    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ADAPTIVE + CODEC XBEE</v>
@@ -13723,7 +13723,7 @@
       </c>
       <c r="O33" s="28"/>
     </row>
-    <row r="34" spans="1:15">
+    <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="4" t="str">
         <f t="shared" si="0"/>
         <v>ADAPTIVE + CODEC XBEE</v>
@@ -13774,7 +13774,7 @@
       </c>
       <c r="O34" s="28"/>
     </row>
-    <row r="35" spans="1:15">
+    <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="4" t="str">
         <f t="shared" si="0"/>
         <v>CODEC XBEE</v>
@@ -13825,7 +13825,7 @@
       </c>
       <c r="O35" s="28"/>
     </row>
-    <row r="36" spans="1:15">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="str">
         <f t="shared" si="0"/>
         <v>CODEC XBEE</v>
@@ -13876,7 +13876,7 @@
       </c>
       <c r="O36" s="28"/>
     </row>
-    <row r="37" spans="1:15">
+    <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="str">
         <f t="shared" si="0"/>
         <v>CODEC + ENERGY XBEE</v>
@@ -13927,7 +13927,7 @@
       </c>
       <c r="O37" s="28"/>
     </row>
-    <row r="38" spans="1:15">
+    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="str">
         <f t="shared" si="0"/>
         <v>CODEC + ENERGY + ADAPTATIVE XBEE</v>
